--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486863_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486863_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9444</v>
+        <v>3.8272</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4368</v>
+        <v>5.0528</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.4923</v>
+        <v>-1.2256</v>
       </c>
       <c r="G2" t="n">
         <v>3.8677</v>
@@ -610,13 +610,13 @@
         <v>2.6694</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.3599</v>
+        <v>-1.477</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.0699</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.6739</v>
+        <v>-1.4071</v>
       </c>
       <c r="V2" t="n">
         <v>0.8205</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3149</v>
+        <v>1.0476</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2059</v>
+        <v>1.5092</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8911</v>
+        <v>-0.4616</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0635</v>
+        <v>-0.1245</v>
       </c>
       <c r="H3" t="n">
-        <v>2.8709</v>
+        <v>-0.2984</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.8074</v>
+        <v>0.1739</v>
       </c>
       <c r="J3" t="n">
-        <v>2.594</v>
+        <v>-0.5566</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4756</v>
+        <v>-0.6355</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1184</v>
+        <v>0.0789</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5305</v>
+        <v>0.4321</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3953</v>
+        <v>0.3371</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9258</v>
+        <v>0.095</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1779</v>
+        <v>0.1802</v>
       </c>
       <c r="T3" t="n">
-        <v>0.612</v>
+        <v>0.4067</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.2265</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.4189</v>
+        <v>-0.2402</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4189</v>
+        <v>-1.8993</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.8047</v>
+        <v>0.8215</v>
       </c>
       <c r="E4" t="n">
-        <v>1.207</v>
+        <v>2.6829</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4023</v>
+        <v>-1.8614</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.1245</v>
+        <v>1.0635</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2984</v>
+        <v>2.8709</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1739</v>
+        <v>-1.8074</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5566</v>
+        <v>2.594</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6355</v>
+        <v>2.4756</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0789</v>
+        <v>0.1184</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4321</v>
+        <v>-1.5305</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3371</v>
+        <v>0.3953</v>
       </c>
       <c r="O4" t="n">
-        <v>0.095</v>
+        <v>-1.9258</v>
       </c>
       <c r="P4" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2321</v>
+        <v>1.8481</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.06270000000000001</v>
+        <v>-0.6712</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1045</v>
+        <v>0.089</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1672</v>
+        <v>-0.7602</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2402</v>
+        <v>-1.4189</v>
       </c>
       <c r="W4" t="n">
-        <v>1.6591</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8993</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1856</v>
+        <v>-0.09909999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0498</v>
+        <v>-0.0227</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1357</v>
+        <v>-0.0765</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4986</v>
@@ -844,13 +844,13 @@
         <v>2.8748</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7005</v>
+        <v>-0.6141</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0191</v>
+        <v>0.0463</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7196</v>
+        <v>-0.6604</v>
       </c>
       <c r="V5" t="n">
         <v>1.1922</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>A. BUTKO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2185</v>
+        <v>-0.4169</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9102</v>
+        <v>-0.0659</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1288</v>
+        <v>-0.351</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0938</v>
+        <v>-0.0314</v>
       </c>
       <c r="H6" t="n">
-        <v>4.3605</v>
+        <v>0.2238</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.4543</v>
+        <v>-0.2552</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1808</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8518</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.671</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.2746</v>
+        <v>-0.0314</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5087</v>
+        <v>0.2238</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.7833</v>
+        <v>-0.2552</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4641</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2471</v>
+        <v>-0.3855</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7746</v>
+        <v>-0.0659</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.0218</v>
+        <v>-0.3196</v>
       </c>
       <c r="V6" t="n">
-        <v>0.7117</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.0082</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2965</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BUTKO</t>
+          <t>T. TRIFONOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4762</v>
+        <v>-0.8455</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0659</v>
+        <v>0.7287</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4103</v>
+        <v>-1.5742</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.0314</v>
+        <v>0.8895</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2238</v>
+        <v>1.2685</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2552</v>
+        <v>-0.3789</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.8604000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1.5183</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.6579</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0314</v>
+        <v>0.0291</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2238</v>
+        <v>-0.2498</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2552</v>
+        <v>0.2789</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.2053</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4448</v>
+        <v>-0.1724</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0659</v>
+        <v>-0.1317</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3789</v>
+        <v>-0.0407</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="8">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T. TRIFONOV</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9048</v>
+        <v>-1.0949</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7287</v>
+        <v>1.271</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6335</v>
+        <v>-2.3659</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8895</v>
+        <v>-1.0938</v>
       </c>
       <c r="H9" t="n">
-        <v>1.2685</v>
+        <v>4.3605</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3789</v>
+        <v>-5.4543</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8604000000000001</v>
+        <v>1.1808</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5183</v>
+        <v>3.8518</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6579</v>
+        <v>-2.671</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0291</v>
+        <v>-2.2746</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2498</v>
+        <v>0.5087</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2789</v>
+        <v>-2.7833</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2053</v>
+        <v>0.4107</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2053</v>
+        <v>2.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2317</v>
+        <v>-1.1235</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1317</v>
+        <v>0.1354</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0999</v>
+        <v>-1.2589</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.7679</v>
+        <v>0.7117</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.0082</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.7679</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.5265</v>
+        <v>-3.8347</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9509</v>
+        <v>-3.4666</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5756</v>
+        <v>-0.3681</v>
       </c>
       <c r="G10" t="n">
         <v>-1.6381</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8884</v>
+        <v>-0.1966</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5851</v>
+        <v>-0.1008</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3033</v>
+        <v>-0.0958</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1786</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.4122</v>
+        <v>-6.5019</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.9721</v>
+        <v>-4.7358</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.44</v>
+        <v>-1.7661</v>
       </c>
       <c r="G11" t="n">
         <v>-6.1312</v>
@@ -1312,13 +1312,13 @@
         <v>2.0534</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3173</v>
+        <v>0.2276</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2167</v>
+        <v>0.4531</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1006</v>
+        <v>-0.2255</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5983000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.9628</v>
+        <v>-6.5378</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.5682</v>
+        <v>-4.0839</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.3946</v>
+        <v>-2.4539</v>
       </c>
       <c r="G12" t="n">
         <v>-1.047</v>
@@ -1390,13 +1390,13 @@
         <v>0.616</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5393</v>
+        <v>-0.1143</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7169</v>
+        <v>-0.2326</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1776</v>
+        <v>0.1183</v>
       </c>
       <c r="V12" t="n">
         <v>-1.8858</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-15.5109</v>
+        <v>-14.5228</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8226</v>
+        <v>-1.834599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-12.6882</v>
+        <v>-12.6883</v>
       </c>
       <c r="G13" t="n">
         <v>-6.632199999999999</v>
@@ -1441,10 +1441,10 @@
         <v>-17.7596</v>
       </c>
       <c r="J13" t="n">
-        <v>6.028500000000001</v>
+        <v>6.028499999999998</v>
       </c>
       <c r="K13" t="n">
-        <v>9.412100000000001</v>
+        <v>9.412099999999999</v>
       </c>
       <c r="L13" t="n">
         <v>-3.3831</v>
@@ -1468,19 +1468,19 @@
         <v>15.4006</v>
       </c>
       <c r="S13" t="n">
-        <v>-5.540299999999999</v>
+        <v>-4.5521</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5246</v>
+        <v>0.4636999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.0157</v>
+        <v>-5.0159</v>
       </c>
       <c r="V13" t="n">
         <v>-4.3653</v>
       </c>
       <c r="W13" t="n">
-        <v>6.047000000000001</v>
+        <v>6.047</v>
       </c>
       <c r="X13" t="n">
         <v>-10.4124</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.7084</v>
+        <v>12.4233</v>
       </c>
       <c r="E14" t="n">
-        <v>10.6228</v>
+        <v>11.0412</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0856</v>
+        <v>1.3821</v>
       </c>
       <c r="G14" t="n">
         <v>7.6262</v>
@@ -1546,13 +1546,13 @@
         <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1395</v>
+        <v>0.5754</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1045</v>
+        <v>0.5229</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.244</v>
+        <v>0.0524</v>
       </c>
       <c r="V14" t="n">
         <v>4.0164</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7929</v>
+        <v>6.6029</v>
       </c>
       <c r="E15" t="n">
-        <v>4.2997</v>
+        <v>3.8813</v>
       </c>
       <c r="F15" t="n">
-        <v>2.4931</v>
+        <v>2.7215</v>
       </c>
       <c r="G15" t="n">
         <v>5.2807</v>
@@ -1624,13 +1624,13 @@
         <v>2.0534</v>
       </c>
       <c r="S15" t="n">
-        <v>0.4854</v>
+        <v>0.2954</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7437</v>
+        <v>0.3253</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2583</v>
+        <v>-0.0299</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.1902</v>
+        <v>2.2784</v>
       </c>
       <c r="E16" t="n">
-        <v>2.9247</v>
+        <v>1.9832</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2655</v>
+        <v>0.2951</v>
       </c>
       <c r="G16" t="n">
         <v>2.8101</v>
@@ -1702,13 +1702,13 @@
         <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6121</v>
+        <v>0.7003</v>
       </c>
       <c r="T16" t="n">
-        <v>1.9331</v>
+        <v>0.9916</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.321</v>
+        <v>-0.2913</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>J. RODRIGUEZ JIMENEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9303</v>
+        <v>1.5805</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0169</v>
+        <v>0.9243</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9134</v>
+        <v>0.6561</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.728</v>
+        <v>0.0985</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.6935</v>
+        <v>-1.6092</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9656</v>
+        <v>1.7077</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.258</v>
+        <v>0.7423</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.363</v>
+        <v>-0.639</v>
       </c>
       <c r="L17" t="n">
-        <v>0.105</v>
+        <v>1.3813</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4699</v>
+        <v>-0.6438</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3305</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8606</v>
+        <v>0.3264</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0534</v>
+        <v>-0.2053</v>
       </c>
       <c r="R17" t="n">
-        <v>0.616</v>
+        <v>1.2321</v>
       </c>
       <c r="S17" t="n">
-        <v>2.9868</v>
+        <v>0.215</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3283</v>
+        <v>0.1471</v>
       </c>
       <c r="U17" t="n">
-        <v>0.6585</v>
+        <v>0.0679</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1088</v>
+        <v>0.2402</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ JIMENEZ</t>
+          <t>G. BLAT BAEZA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.768</v>
+        <v>1.3766</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1921</v>
+        <v>-0.4523</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5759</v>
+        <v>1.8289</v>
       </c>
       <c r="G18" t="n">
-        <v>0.0985</v>
+        <v>-0.079</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.6092</v>
+        <v>-2.66</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7077</v>
+        <v>2.581</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7423</v>
+        <v>-0.2981</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.639</v>
+        <v>-2.6921</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3813</v>
+        <v>2.394</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6438</v>
+        <v>0.2191</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9703000000000001</v>
+        <v>0.0321</v>
       </c>
       <c r="O18" t="n">
-        <v>0.3264</v>
+        <v>0.187</v>
       </c>
       <c r="P18" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2053</v>
+        <v>-1.2321</v>
       </c>
       <c r="R18" t="n">
-        <v>1.2321</v>
+        <v>1.6427</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5974</v>
+        <v>0.1065</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5851</v>
+        <v>-0.1008</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0123</v>
+        <v>0.2074</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2402</v>
+        <v>0.9384</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2402</v>
+        <v>1.1786</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. BLAT BAEZA</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6409</v>
+        <v>0.4298</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8707</v>
+        <v>1.9865</v>
       </c>
       <c r="F19" t="n">
-        <v>1.5116</v>
+        <v>-1.5567</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.079</v>
+        <v>-0.6965</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.66</v>
+        <v>-0.2888</v>
       </c>
       <c r="I19" t="n">
-        <v>2.581</v>
+        <v>-0.4077</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2981</v>
+        <v>1.0133</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.6921</v>
+        <v>0.9344</v>
       </c>
       <c r="L19" t="n">
-        <v>2.394</v>
+        <v>0.0789</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2191</v>
+        <v>-1.7098</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0321</v>
+        <v>-1.2231</v>
       </c>
       <c r="O19" t="n">
-        <v>0.187</v>
+        <v>-0.4866</v>
       </c>
       <c r="P19" t="n">
+        <v>0.2053</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.2053</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.4107</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.2321</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.6427</v>
-      </c>
       <c r="S19" t="n">
-        <v>-0.6292</v>
+        <v>0.2227</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5192</v>
+        <v>-0.0001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.11</v>
+        <v>0.2228</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9384</v>
+        <v>0.6982</v>
       </c>
       <c r="W19" t="n">
         <v>1.1786</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2402</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5937</v>
+        <v>0.0115</v>
       </c>
       <c r="E20" t="n">
-        <v>2.0911</v>
+        <v>-0.7154</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4974</v>
+        <v>0.7268</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.6965</v>
+        <v>-0.728</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2888</v>
+        <v>-1.6935</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4077</v>
+        <v>0.9656</v>
       </c>
       <c r="J20" t="n">
-        <v>1.0133</v>
+        <v>-0.258</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9344</v>
+        <v>-0.363</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0789</v>
+        <v>0.105</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.7098</v>
+        <v>-0.4699</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2231</v>
+        <v>-1.3305</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.4866</v>
+        <v>0.8606</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2053</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.2053</v>
+        <v>-2.0534</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4107</v>
+        <v>0.616</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3866</v>
+        <v>2.068</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1045</v>
+        <v>1.5961</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2821</v>
+        <v>0.4719</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6982</v>
+        <v>0.1088</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4805</v>
+        <v>0.1088</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4606</v>
+        <v>-0.7005</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6986</v>
+        <v>0.3388</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2381</v>
+        <v>-1.0393</v>
       </c>
       <c r="G21" t="n">
         <v>-3.4621</v>
@@ -2092,13 +2092,13 @@
         <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>2.3601</v>
+        <v>1.199</v>
       </c>
       <c r="T21" t="n">
-        <v>2.1384</v>
+        <v>0.7786</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2217</v>
+        <v>0.4204</v>
       </c>
       <c r="V21" t="n">
         <v>1.7679</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8938</v>
+        <v>-0.9799</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3183</v>
+        <v>-0.518</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4246</v>
+        <v>-0.4619</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3371</v>
+        <v>0.7698</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5187</v>
+        <v>-2.1928</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1816</v>
+        <v>2.9626</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1234</v>
+        <v>2.1946</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0973</v>
+        <v>-0.2783</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0261</v>
+        <v>2.4729</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2137</v>
+        <v>-1.4248</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4214</v>
+        <v>-1.9145</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2077</v>
+        <v>0.4897</v>
       </c>
       <c r="P22" t="n">
+        <v>-1.8481</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-3.0801</v>
+      </c>
+      <c r="R22" t="n">
         <v>1.2321</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-1.0267</v>
-      </c>
-      <c r="R22" t="n">
-        <v>2.2588</v>
-      </c>
       <c r="S22" t="n">
-        <v>-0.4075</v>
+        <v>0.4475</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.7169</v>
+        <v>0.4764</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3093</v>
+        <v>-0.0289</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.0554</v>
+        <v>-0.3491</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6982</v>
+        <v>-0.1088</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3573</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.385</v>
+        <v>-1.9357</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9824</v>
+        <v>-2.0045</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4026</v>
+        <v>0.0689</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7698</v>
+        <v>0.3371</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.1928</v>
+        <v>0.5187</v>
       </c>
       <c r="I23" t="n">
-        <v>2.9626</v>
+        <v>-0.1816</v>
       </c>
       <c r="J23" t="n">
-        <v>2.1946</v>
+        <v>0.1234</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2783</v>
+        <v>0.0973</v>
       </c>
       <c r="L23" t="n">
-        <v>2.4729</v>
+        <v>0.0261</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4248</v>
+        <v>0.2137</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.9145</v>
+        <v>0.4214</v>
       </c>
       <c r="O23" t="n">
-        <v>0.4897</v>
+        <v>-0.2077</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8481</v>
+        <v>1.2321</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.0801</v>
+        <v>-1.0267</v>
       </c>
       <c r="R23" t="n">
-        <v>1.2321</v>
+        <v>2.2588</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9577</v>
+        <v>-0.4494</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9881</v>
+        <v>-0.4031</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0304</v>
+        <v>-0.0464</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3491</v>
+        <v>-3.0554</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.1088</v>
+        <v>-0.6982</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2952</v>
+        <v>-4.8785</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9861</v>
+        <v>-3.7769</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3091</v>
+        <v>-1.1016</v>
       </c>
       <c r="G24" t="n">
         <v>-5.325</v>
@@ -2326,13 +2326,13 @@
         <v>0.8214</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4405</v>
+        <v>0.8572</v>
       </c>
       <c r="T24" t="n">
-        <v>0.4725</v>
+        <v>0.6817</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.032</v>
+        <v>0.1755</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>15.511</v>
+        <v>16.2084</v>
       </c>
       <c r="E25" t="n">
-        <v>12.6884</v>
+        <v>12.6882</v>
       </c>
       <c r="F25" t="n">
-        <v>2.822500000000001</v>
+        <v>3.5199</v>
       </c>
       <c r="G25" t="n">
-        <v>6.631800000000001</v>
+        <v>6.631799999999999</v>
       </c>
       <c r="H25" t="n">
         <v>-11.1277</v>
@@ -2404,13 +2404,13 @@
         <v>14.3741</v>
       </c>
       <c r="S25" t="n">
-        <v>5.540200000000001</v>
+        <v>6.2376</v>
       </c>
       <c r="T25" t="n">
-        <v>5.015700000000001</v>
+        <v>5.0157</v>
       </c>
       <c r="U25" t="n">
-        <v>0.5244</v>
+        <v>1.2218</v>
       </c>
       <c r="V25" t="n">
         <v>4.365399999999999</v>
